--- a/Aston Martin Financial Model.xlsx
+++ b/Aston Martin Financial Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanishq/Documents/Aston Martin Equity Research Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8E61CB-9DE9-D84C-9359-A90AEC4D90AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE5F46F-A120-0848-ADDA-88C6FAAB8D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{AA98E4D7-9542-9840-9FD2-96EB0DAA6529}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{AA98E4D7-9542-9840-9FD2-96EB0DAA6529}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
   <si>
     <t>2022A</t>
   </si>
@@ -208,20 +208,105 @@
     <t>Working Capital Change (%Revenue)</t>
   </si>
   <si>
-    <t>Other Operating Cash Adjustments (&amp;Revenue)</t>
+    <t>Other Operating Cash Adjustments (%Revenue)</t>
+  </si>
+  <si>
+    <t>ASTON MARTIN LAGONDA</t>
+  </si>
+  <si>
+    <t>Financial Model &amp; Investment Analysis</t>
+  </si>
+  <si>
+    <t>Historical Analysis: 2022-2025 | Forecast: 2026-2030</t>
+  </si>
+  <si>
+    <t>Prepared by Tanishq Belide</t>
+  </si>
+  <si>
+    <t>Model Overview</t>
+  </si>
+  <si>
+    <t>Historical Financials</t>
+  </si>
+  <si>
+    <t>Cash Flow Forecast</t>
+  </si>
+  <si>
+    <t>Net Debt &amp; Interest Schedule</t>
+  </si>
+  <si>
+    <t>DCF Valuation - In Progress</t>
+  </si>
+  <si>
+    <t>Comparable Companies - In Progress</t>
+  </si>
+  <si>
+    <t>Sensitivity Analysis - In Progress</t>
+  </si>
+  <si>
+    <t>Operating &amp; Revenue Forecast</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -247,12 +332,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,9 +686,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E19AE2-E316-6B42-A19D-C4B5E9D15DDF}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:B21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="41.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="19" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B6" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B10" s="6">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -604,7 +778,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B1" t="s">
@@ -620,366 +794,414 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="11"/>
+    </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="8">
         <v>1381.5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>1633</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>1583.9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="8">
         <v>1257.7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3">
+      <c r="B4" s="11"/>
+      <c r="C4" s="12">
         <f>C3/B3-1</f>
         <v>0.18204849800941014</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="12">
         <f t="shared" ref="D4:E4" si="0">D3/C3-1</f>
         <v>-3.006736068585425E-2</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="12">
         <f t="shared" si="0"/>
         <v>-0.20594734516067936</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="8">
         <v>-930.8</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>-993.6</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>-1000</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <v>-887.9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="8">
         <v>450.7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>639</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="8">
         <v>583.9</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="8">
         <v>369.8</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="12">
         <f>B6/B3</f>
         <v>0.32623959464350344</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="12">
         <f t="shared" ref="C7:E7" si="1">C6/C3</f>
         <v>0.39130434782608697</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="12">
         <f t="shared" si="1"/>
         <v>0.36864701054359489</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="12">
         <f t="shared" si="1"/>
         <v>0.29402878269857674</v>
       </c>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>-568.6</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>-718.9</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="8">
         <v>-666.7</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="8">
         <v>-559</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="8">
         <v>-117.9</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="8">
         <v>-79.7</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="8">
         <v>-82.8</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="8">
         <v>-189.2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="12">
         <f>B10/B3</f>
         <v>-8.534201954397394E-2</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="12">
         <f t="shared" ref="C11:E11" si="2">C10/C3</f>
         <v>-4.8805878750765461E-2</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="12">
         <f t="shared" si="2"/>
         <v>-5.2276027526990336E-2</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="12">
         <f t="shared" si="2"/>
         <v>-0.15043333068299275</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="8">
         <v>-141.80000000000001</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="8">
         <v>-111.2</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="8">
         <v>-99.5</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="8">
         <v>-259.2</v>
       </c>
     </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="8">
         <v>-495</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="8">
         <v>-239.8</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="8">
         <v>-289.10000000000002</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="8">
         <v>-363.9</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="8">
         <v>-32.700000000000003</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="8">
         <v>13</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="8">
         <v>-34.4</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="8">
         <v>-129.1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="8">
         <v>-527.70000000000005</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="8">
         <v>-226.8</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="8">
         <v>-323.5</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="8">
         <v>-493</v>
       </c>
     </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="8">
         <v>190.2</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="8">
         <v>305.89999999999998</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="8">
         <v>271</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="8">
         <v>108.1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="12">
         <f>B18/B3</f>
         <v>0.13767643865363735</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="12">
         <f t="shared" ref="C19:E19" si="3">C18/C3</f>
         <v>0.1873239436619718</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="12">
         <f t="shared" si="3"/>
         <v>0.17109666014268576</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="12">
         <f t="shared" si="3"/>
         <v>8.5950544644986873E-2</v>
       </c>
     </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="11"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="8">
         <v>127.1</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="8">
         <v>145.9</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="8">
         <v>123.9</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="8">
         <v>74.099999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="10">
         <v>-286.89999999999998</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="8">
         <v>-396.9</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="8">
         <v>-400.6</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="8">
         <v>-341</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="8">
         <v>-298.8</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="8">
         <v>-360</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="8">
         <v>-391.6</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="8">
         <v>-409.9</v>
       </c>
     </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="8">
         <v>583.29999999999995</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="8">
         <v>392.4</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="8">
         <v>359.6</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="8">
         <v>249.9</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D26">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8">
         <v>1387.3</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="8">
         <v>1500.2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="8">
         <v>765.5</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="8">
         <v>814.3</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="8">
         <v>1162.7</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="8">
         <v>1380.3</v>
       </c>
     </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="11"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="8">
         <v>6412</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="8">
         <v>6620</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="8">
         <v>6030</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="8">
         <v>5448</v>
       </c>
     </row>
@@ -1001,83 +1223,98 @@
       <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="8" t="s">
         <v>30</v>
       </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="8">
         <v>5450</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>5700</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>5900</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="8">
         <v>6050</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="8">
         <v>6150</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="3">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12">
         <f>C3/B3-1</f>
         <v>4.587155963302747E-2</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="12">
         <f>D3/C3-1</f>
         <v>3.5087719298245723E-2</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="12">
         <f>E3/D3-1</f>
         <v>2.5423728813559254E-2</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="12">
         <f>F3/E3-1</f>
         <v>1.6528925619834656E-2</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="11">
         <v>225</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="11">
         <f>B6*(1+C7)</f>
         <v>236.25</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="11">
         <f>C6*(1+D7)</f>
         <v>245.70000000000002</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="11">
         <f>D6*(1+E7)</f>
         <v>254.29949999999999</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="11">
         <f>E6*(1+F7)</f>
         <v>261.92848500000002</v>
       </c>
@@ -1086,130 +1323,150 @@
       <c r="A7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="13">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="14">
         <v>0.05</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="14">
         <v>0.04</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="13">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="14">
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="12">
         <f>((B3*B6)/1000+B18)/'Historical Financials'!E3-1</f>
         <v>6.6430786356046712E-2</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="12">
         <f>((C3*C6)/1000+C18)/((B3*B6)/1000+B18)-1</f>
         <v>9.3476234855545126E-2</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="12">
         <f>((D3*D6)/1000+D18)/((C3*C6)/1000+C18)-1</f>
         <v>7.3641864825705339E-2</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="12">
         <f>((E3*E6)/1000+E18)/((D3*D6)/1000+D18)-1</f>
         <v>5.9621609520966734E-2</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="12">
         <f>((F3*F6)/1000+F18)/((E3*E6)/1000+E18)-1</f>
         <v>4.6357598212623197E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="9">
         <v>0.37</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="9">
         <v>0.38500000000000001</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="9">
         <v>0.39500000000000002</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="9">
         <v>0.4</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="9">
         <v>0.40500000000000003</v>
       </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="8">
         <v>-535</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="8">
         <v>-545</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="8">
         <v>-550</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="8">
         <v>-555</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="8">
         <v>-565</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="12">
         <f>B10+B12/(((B3*B6)/1000)+B18)</f>
         <v>-2.8881640260950636E-2</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="12">
         <f>C10+C12/(((C3*C6)/1000)+C18)</f>
         <v>1.3398534049262778E-2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="12">
         <f>D10+D12/(((D3*D6)/1000)+D18)</f>
         <v>4.5711595739951649E-2</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="12">
         <f>E10+E12/(((E3*E6)/1000)+E18)</f>
         <v>6.7368284845543303E-2</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="12">
         <f>F10+F12/(((F3*F6)/1000)+F18)</f>
         <v>8.1377292074994556E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+    </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="13">
         <v>0.23599999999999999</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="13">
         <v>0.23599999999999999</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="13">
         <v>0.23599999999999999</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="13">
         <v>0.23600000000000002</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="13">
         <v>0.23600000000000002</v>
       </c>
     </row>
@@ -1217,19 +1474,19 @@
       <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="8">
         <v>-340</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="8">
         <v>-340</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="8">
         <v>-340</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="8">
         <v>-340</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="8">
         <v>-340</v>
       </c>
     </row>
@@ -1237,19 +1494,19 @@
       <c r="A17" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="14">
         <v>0.25</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="14">
         <v>0.25</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="14">
         <v>0.25</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="14">
         <v>0.25</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="14">
         <v>0.25</v>
       </c>
     </row>
@@ -1257,59 +1514,66 @@
       <c r="A18" t="s">
         <v>42</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="8">
         <v>115</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="8">
         <v>120</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="8">
         <v>125</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="8">
         <v>130</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="8">
         <v>135</v>
       </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="2">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.68500000000000005</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.68500000000000005</v>
+      <c r="B20" s="13">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="C20" s="13">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="D20" s="13">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="E20" s="13">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="F20" s="13">
+        <v>-3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="13">
         <v>0.105</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="13">
         <v>0.105</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="13">
         <v>0.105</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="13">
         <v>0.105</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="13">
         <v>0.105</v>
       </c>
     </row>
@@ -1317,19 +1581,19 @@
       <c r="A22" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="14">
         <v>-0.01</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="14">
         <v>-0.01</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="14">
         <v>-0.01</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="14">
         <v>-0.01</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="14">
         <v>-0.01</v>
       </c>
     </row>
@@ -1382,19 +1646,19 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="15">
         <f>'Historical Financials'!B3</f>
         <v>1381.5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="15">
         <f>'Historical Financials'!C3</f>
         <v>1633</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="15">
         <f>'Historical Financials'!D3</f>
         <v>1583.9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="15">
         <f>'Historical Financials'!E3</f>
         <v>1257.7</v>
       </c>
@@ -1419,39 +1683,39 @@
         <v>1745.8601827500004</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="1">
         <f>C3/B3-1</f>
         <v>0.18204849800941014</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <f t="shared" ref="D4:E4" si="0">D3/C3-1</f>
         <v>-3.006736068585425E-2</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <f t="shared" si="0"/>
         <v>-0.20594734516067936</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="17">
         <f>Assumptions!B9</f>
         <v>6.6430786356046712E-2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="17">
         <f>Assumptions!C9</f>
         <v>9.3476234855545126E-2</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="17">
         <f>Assumptions!D9</f>
         <v>7.3641864825705339E-2</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="17">
         <f>Assumptions!E9</f>
         <v>5.9621609520966734E-2</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="17">
         <f>Assumptions!F9</f>
         <v>4.6357598212623197E-2</v>
       </c>
@@ -1460,19 +1724,19 @@
       <c r="A6" t="s">
         <v>31</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="15">
         <f>'Historical Financials'!B5</f>
         <v>-930.8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="15">
         <f>'Historical Financials'!C5</f>
         <v>-993.6</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="15">
         <f>'Historical Financials'!D5</f>
         <v>-1000</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="15">
         <f>'Historical Financials'!E5</f>
         <v>-887.9</v>
       </c>
@@ -1501,19 +1765,19 @@
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="15">
         <f>'Historical Financials'!B6</f>
         <v>450.7</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="15">
         <f>'Historical Financials'!C6</f>
         <v>639</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="15">
         <f>'Historical Financials'!D6</f>
         <v>583.9</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="15">
         <f>'Historical Financials'!E6</f>
         <v>369.8</v>
       </c>
@@ -1542,39 +1806,39 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <f>B7/B3</f>
         <v>0.32623959464350344</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <f t="shared" ref="C8:E8" si="1">C7/C3</f>
         <v>0.39130434782608697</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <f t="shared" si="1"/>
         <v>0.36864701054359489</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.29402878269857674</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="17">
         <f>Assumptions!B10</f>
         <v>0.37</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="17">
         <f>Assumptions!C10</f>
         <v>0.38500000000000001</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="17">
         <f>Assumptions!D10</f>
         <v>0.39500000000000002</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="17">
         <f>Assumptions!E10</f>
         <v>0.4</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="17">
         <f>Assumptions!F10</f>
         <v>0.40500000000000003</v>
       </c>
@@ -1583,39 +1847,39 @@
       <c r="A10" t="s">
         <v>32</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="15">
         <f>'Historical Financials'!B9</f>
         <v>-568.6</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="15">
         <f>'Historical Financials'!C9</f>
         <v>-718.9</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="15">
         <f>'Historical Financials'!D9</f>
         <v>-666.7</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="15">
         <f>'Historical Financials'!E9</f>
         <v>-559</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="15">
         <f>Assumptions!B12</f>
         <v>-535</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="15">
         <f>Assumptions!C12</f>
         <v>-545</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="15">
         <f>Assumptions!D12</f>
         <v>-550</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="15">
         <f>Assumptions!E12</f>
         <v>-555</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="15">
         <f>Assumptions!F12</f>
         <v>-565</v>
       </c>
@@ -1649,19 +1913,19 @@
       <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="15">
         <f>'Historical Financials'!B10</f>
         <v>-117.9</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="15">
         <f>'Historical Financials'!C10</f>
         <v>-79.7</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="15">
         <f>'Historical Financials'!D10</f>
         <v>-82.8</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="15">
         <f>'Historical Financials'!E10</f>
         <v>-189.2</v>
       </c>
@@ -1690,72 +1954,72 @@
       <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <f>B12/B3</f>
         <v>-8.534201954397394E-2</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <f>C12/C3</f>
         <v>-4.8805878750765461E-2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
         <f>D12/D3</f>
         <v>-5.2276027526990336E-2</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <f>E12/E3</f>
         <v>-0.15043333068299275</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="1">
         <f>F12/F3</f>
         <v>-2.8881640260950615E-2</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="1">
         <f>G12/G3</f>
         <v>1.3398534049262757E-2</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="1">
         <f>H12/H3</f>
         <v>4.5711595739951656E-2</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="1">
         <f>I12/I3</f>
         <v>6.7368284845543316E-2</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="1">
         <f>J12/J3</f>
         <v>8.1377292074994612E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="16">
         <v>-23.9</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="16">
         <v>-31.5</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="16">
         <v>-16.7</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="16">
         <v>-70</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="2">
         <v>0</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <v>0</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="2">
         <v>0</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1763,19 +2027,19 @@
       <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="15">
         <f>B12+B14</f>
         <v>-141.80000000000001</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="15">
         <f t="shared" ref="C15:E15" si="2">C12+C14</f>
         <v>-111.2</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="15">
         <f t="shared" si="2"/>
         <v>-99.5</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="15">
         <f t="shared" si="2"/>
         <v>-259.2</v>
       </c>
@@ -1804,16 +2068,16 @@
       <c r="A17" t="s">
         <v>33</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="8">
         <v>-353.2</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="8">
         <v>-128.6</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="8">
         <v>-189.6</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="8">
         <v>-104.7</v>
       </c>
       <c r="F17">
@@ -1841,19 +2105,19 @@
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="15">
         <f>B15+B17</f>
         <v>-495</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="15">
         <f t="shared" ref="C18:E18" si="3">C15+C17</f>
         <v>-239.8</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="15">
         <f t="shared" si="3"/>
         <v>-289.10000000000002</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="15">
         <f t="shared" si="3"/>
         <v>-363.9</v>
       </c>
@@ -1882,19 +2146,19 @@
       <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="15">
         <f>'Historical Financials'!B15</f>
         <v>-32.700000000000003</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="15">
         <f>'Historical Financials'!C15</f>
         <v>13</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="15">
         <f>'Historical Financials'!D15</f>
         <v>-34.4</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="15">
         <f>'Historical Financials'!E15</f>
         <v>-129.1</v>
       </c>
@@ -1964,19 +2228,19 @@
       <c r="A23" t="s">
         <v>19</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="15">
         <f>'Historical Financials'!B18</f>
         <v>190.2</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="15">
         <f>'Historical Financials'!C18</f>
         <v>305.89999999999998</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="15">
         <f>'Historical Financials'!D18</f>
         <v>271</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="15">
         <f>'Historical Financials'!E18</f>
         <v>108.1</v>
       </c>
@@ -2005,39 +2269,39 @@
       <c r="A24" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="1">
         <f>B23/B3</f>
         <v>0.13767643865363735</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="1">
         <f>C23/C3</f>
         <v>0.1873239436619718</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="1">
         <f>D23/D3</f>
         <v>0.17109666014268576</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="1">
         <f>E23/E3</f>
         <v>8.5950544644986873E-2</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="1">
         <f>F23/F3</f>
         <v>0.20711835973904935</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="1">
         <f>G23/G3</f>
         <v>0.24939853404926274</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="1">
         <f>H23/H3</f>
         <v>0.28171159573995164</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="1">
         <f>I23/I3</f>
         <v>0.30336828484554335</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="1">
         <f>J23/J3</f>
         <v>0.31737729207499465</v>
       </c>
@@ -2091,39 +2355,39 @@
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="15">
         <f>'Income Statement'!B23</f>
         <v>190.2</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="15">
         <f>'Income Statement'!C23</f>
         <v>305.89999999999998</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="15">
         <f>'Income Statement'!D23</f>
         <v>271</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="15">
         <f>'Income Statement'!E23</f>
         <v>108.1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="15">
         <f>'Income Statement'!F23</f>
         <v>277.79749999999996</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="15">
         <f>'Income Statement'!G23</f>
         <v>365.77412499999997</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="15">
         <f>'Income Statement'!H23</f>
         <v>443.59153000000009</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="15">
         <f>'Income Statement'!I23</f>
         <v>506.17361610000006</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="15">
         <f>'Income Statement'!J23</f>
         <v>554.09637714275038</v>
       </c>
@@ -2132,94 +2396,98 @@
       <c r="A4" t="s">
         <v>52</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <v>-86</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="8">
         <v>-118</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="8">
         <v>6</v>
+      </c>
+      <c r="F4">
+        <f>'Income Statement'!F3*Assumptions!B22</f>
+        <v>-13.4125</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="8">
         <f>'Historical Financials'!B21</f>
         <v>127.1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <f>'Historical Financials'!C21</f>
         <v>145.9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <f>'Historical Financials'!D21</f>
         <v>123.9</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <f>'Historical Financials'!E21</f>
         <v>74.099999999999994</v>
       </c>
       <c r="F5">
-        <f>F3*Assumptions!B20</f>
-        <v>190.29128749999998</v>
+        <f>F3+F4+('Income Statement'!F3*Assumptions!B20)</f>
+        <v>221.46499999999992</v>
       </c>
       <c r="G5">
-        <f>G3*Assumptions!C20</f>
-        <v>250.55527562500001</v>
+        <f>G3+G4+('Income Statement'!G3*Assumptions!C20)</f>
+        <v>318.84212499999995</v>
       </c>
       <c r="H5">
-        <f>H3*Assumptions!D20</f>
-        <v>303.86019805000006</v>
+        <f>H3+H4+('Income Statement'!H3*Assumptions!D20)</f>
+        <v>393.20337000000006</v>
       </c>
       <c r="I5">
-        <f>I3*Assumptions!E20</f>
-        <v>346.7289270285001</v>
+        <f>I3+I4+('Income Statement'!I3*Assumptions!E20)</f>
+        <v>452.78123290000008</v>
       </c>
       <c r="J5">
-        <f>J3*Assumptions!F20</f>
-        <v>379.55601834278406</v>
+        <f>J3+J4+('Income Statement'!J3*Assumptions!F20)</f>
+        <v>498.22885129475037</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="8">
         <f>'Historical Financials'!B22</f>
         <v>-286.89999999999998</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <f>'Historical Financials'!C22</f>
         <v>-396.9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="8">
         <f>'Historical Financials'!D22</f>
         <v>-400.6</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="8">
         <f>'Historical Financials'!E22</f>
         <v>-341</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="15">
         <f>Assumptions!B16</f>
         <v>-340</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="15">
         <f>Assumptions!C16</f>
         <v>-340</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="15">
         <f>Assumptions!D16</f>
         <v>-340</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="15">
         <f>Assumptions!E16</f>
         <v>-340</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="15">
         <f>Assumptions!F16</f>
         <v>-340</v>
       </c>
@@ -2228,16 +2496,16 @@
       <c r="A7" t="s">
         <v>45</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
         <v>-139</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>-109</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="8">
         <v>-114.9</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="8">
         <v>-143</v>
       </c>
       <c r="F7">
@@ -2246,19 +2514,19 @@
       </c>
       <c r="G7">
         <f t="shared" ref="G7:J7" si="0">G17</f>
-        <v>-175.86872231249998</v>
+        <v>-172.5954825</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>-203.72663421468749</v>
+        <v>-192.93958503750002</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>-228.91261001197967</v>
+        <v>-207.61188761643751</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>-252.24189672524506</v>
+        <v>-217.56910636166344</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2283,48 +2551,48 @@
       </c>
       <c r="F8">
         <f>F5+F6+F7</f>
-        <v>-294.64021250000002</v>
+        <v>-263.46650000000011</v>
       </c>
       <c r="G8">
         <f>G5+G6+G7</f>
-        <v>-265.3134466875</v>
+        <v>-193.75335750000005</v>
       </c>
       <c r="H8">
         <f>H5+H6+H7</f>
-        <v>-239.86643616468743</v>
+        <v>-139.73621503749996</v>
       </c>
       <c r="I8">
         <f t="shared" ref="I8:J8" si="2">I5+I6+I7</f>
-        <v>-222.18368298347957</v>
+        <v>-94.830654716437436</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
-        <v>-212.685878382461</v>
+        <v>-59.340255066913073</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>46</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="15">
         <f>'Historical Financials'!E27</f>
         <v>1380.3</v>
       </c>
       <c r="G11">
         <f>F14</f>
-        <v>1674.9402124999999</v>
+        <v>1643.7665000000002</v>
       </c>
       <c r="H11">
         <f>G14</f>
-        <v>1940.2536591875</v>
+        <v>1837.5198575000002</v>
       </c>
       <c r="I11">
         <f t="shared" ref="I11:J11" si="3">H14</f>
-        <v>2180.1200953521875</v>
+        <v>1977.2560725375001</v>
       </c>
       <c r="J11">
         <f t="shared" si="3"/>
-        <v>2402.3037783356672</v>
+        <v>2072.0867272539376</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -2333,23 +2601,23 @@
       </c>
       <c r="F12">
         <f>F8</f>
-        <v>-294.64021250000002</v>
+        <v>-263.46650000000011</v>
       </c>
       <c r="G12">
         <f>G8</f>
-        <v>-265.3134466875</v>
+        <v>-193.75335750000005</v>
       </c>
       <c r="H12">
         <f t="shared" ref="H12:J12" si="4">H8</f>
-        <v>-239.86643616468743</v>
+        <v>-139.73621503749996</v>
       </c>
       <c r="I12">
         <f t="shared" si="4"/>
-        <v>-222.18368298347957</v>
+        <v>-94.830654716437436</v>
       </c>
       <c r="J12">
         <f t="shared" si="4"/>
-        <v>-212.685878382461</v>
+        <v>-59.340255066913073</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -2358,23 +2626,23 @@
       </c>
       <c r="F13">
         <f>-F12</f>
-        <v>294.64021250000002</v>
+        <v>263.46650000000011</v>
       </c>
       <c r="G13">
         <f>-G12</f>
-        <v>265.3134466875</v>
+        <v>193.75335750000005</v>
       </c>
       <c r="H13">
         <f t="shared" ref="H13:J13" si="5">-H12</f>
-        <v>239.86643616468743</v>
+        <v>139.73621503749996</v>
       </c>
       <c r="I13">
         <f t="shared" si="5"/>
-        <v>222.18368298347957</v>
+        <v>94.830654716437436</v>
       </c>
       <c r="J13">
         <f t="shared" si="5"/>
-        <v>212.685878382461</v>
+        <v>59.340255066913073</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -2383,23 +2651,23 @@
       </c>
       <c r="F14">
         <f>F11+F13</f>
-        <v>1674.9402124999999</v>
+        <v>1643.7665000000002</v>
       </c>
       <c r="G14">
         <f>G11+G13</f>
-        <v>1940.2536591875</v>
+        <v>1837.5198575000002</v>
       </c>
       <c r="H14">
         <f t="shared" ref="H14:J14" si="6">H11+H13</f>
-        <v>2180.1200953521875</v>
+        <v>1977.2560725375001</v>
       </c>
       <c r="I14">
         <f t="shared" si="6"/>
-        <v>2402.3037783356672</v>
+        <v>2072.0867272539376</v>
       </c>
       <c r="J14">
         <f t="shared" si="6"/>
-        <v>2614.9896567181281</v>
+        <v>2131.4269823208506</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -2408,46 +2676,46 @@
       </c>
       <c r="F15">
         <f>(F11+F14)/2</f>
-        <v>1527.6201062499999</v>
+        <v>1512.03325</v>
       </c>
       <c r="G15">
         <f t="shared" ref="G15:J15" si="7">(G11+G14)/2</f>
-        <v>1807.5969358437501</v>
+        <v>1740.6431787500001</v>
       </c>
       <c r="H15">
         <f t="shared" si="7"/>
-        <v>2060.1868772698435</v>
+        <v>1907.38796501875</v>
       </c>
       <c r="I15">
         <f t="shared" si="7"/>
-        <v>2291.2119368439271</v>
+        <v>2024.6713998957189</v>
       </c>
       <c r="J15">
         <f t="shared" si="7"/>
-        <v>2508.6467175268976</v>
+        <v>2101.7568547873943</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="18">
         <f>Assumptions!B21</f>
         <v>0.105</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="18">
         <f>Assumptions!C21</f>
         <v>0.105</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="18">
         <f>Assumptions!D21</f>
         <v>0.105</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="18">
         <f>Assumptions!E21</f>
         <v>0.105</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="18">
         <f>Assumptions!F21</f>
         <v>0.105</v>
       </c>
@@ -2462,19 +2730,19 @@
       </c>
       <c r="G17">
         <f>-G11*Assumptions!C21</f>
-        <v>-175.86872231249998</v>
+        <v>-172.5954825</v>
       </c>
       <c r="H17">
         <f>-H11*Assumptions!D21</f>
-        <v>-203.72663421468749</v>
+        <v>-192.93958503750002</v>
       </c>
       <c r="I17">
         <f>-I11*Assumptions!E21</f>
-        <v>-228.91261001197967</v>
+        <v>-207.61188761643751</v>
       </c>
       <c r="J17">
         <f>-J11*Assumptions!F21</f>
-        <v>-252.24189672524506</v>
+        <v>-217.56910636166344</v>
       </c>
     </row>
   </sheetData>
